--- a/docs/ADaM_Traceability.xlsx
+++ b/docs/ADaM_Traceability.xlsx
@@ -1521,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="43.54296875" customWidth="1" min="1" max="1"/>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Latest treatment end date per subject converted from ISO 8601 character format to SAS numeric date.</t>
+          <t>Latest available treatment end date per subject, converted from ISO 8601 character format to a SAS numeric date. When a subject's final EXENDTC was missing, DM.RFENDTC (carried into ADSL as RFENDT) was used as the fallback treatment end date.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Date validation, missing value assessment, investigation of missing treatment end dates, and PROC COMPARE.</t>
+          <t>Date validation, missing value assessment, investigation of missing treatment end dates, verification of the RFENDTC fallback logic, and PROC COMPARE.</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Calculated as TRTEDT − TRTSDT + 1. Missing treatment dates resulted in missing treatment duration.</t>
+          <t>Calculated as TRTEDT - TRTSDT + 1, using TRTSDT (earliest treatment start date) and TRTEDT (latest treatment end date, including the RFENDTC fallback described above). Missing treatment dates resulted in missing treatment duration.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1909,6 +1909,9 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -1921,6 +1924,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1988,7 +1993,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Copied from SDTM.AE and retained through the build (intermediate working dataset ADAE_STEP5) into the final ADAE.</t>
+          <t>Copied from SDTM.AE into an intermediate dataset (ae_dates / adae0) and carried through to the final ADAM.ADAE in 04_build_adae.sas.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2015,7 +2020,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Copied from SDTM.AE and retained through the build (intermediate working dataset ADAE_STEP5) into the final ADAE, after merging with ADSL by USUBJID.</t>
+          <t>Copied from SDTM.AE and carried through the build (ae_dates -&gt; adae0 -&gt; ADAM.ADAE in 04_build_adae.sas), after merging with ADSL by USUBJID.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2884,7 +2889,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Assigned "Dermatologic Event Occurred" for CNSR=0 and "Study Completion Date" for CNSR=1.</t>
+          <t>Assigned "Dematologic Event Occured" for CNSR=0 and "Study Completion Date" for CNSR=1. The event-occurred text intentionally reproduces the sponsor reference dataset's original spelling (not "Dermatologic Event Occurred") so PROC COMPARE matches the reference exactly - see the comment in 05_build_adtte.sas.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3179,22 +3184,22 @@
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Missing TRTEDT</t>
+          <t>Missing TRTEDT (Historical - not applicable to current code)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Reference dataset contains complete censoring information.</t>
+          <t>Reference dataset contains complete censoring information (0 missing TRTEDT).</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Two censored subjects had missing TRTEDT, resulting in missing ADT and AVAL.</t>
+          <t>TRTEDT falls back to ADSL.RFENDT (from DM.RFENDTC) whenever a subject's last dosing interval has a missing EXENDTC. All 6 such subjects in the source EX data have a non-missing RFENDTC, so TRTEDT is not missing for any subject in the current 03_build_adsl.sas logic.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Source data limitation rather than a programming issue.</t>
+          <t>This row described an earlier draft before the RFENDTC fallback existed. In the current code, ADSL/ADTTE both show 0 missing TRTEDT/ADT/AVAL, consistent with the 0-unequal-records PROC COMPARE result already reported for ADSL and ADTTE. Kept for history only - there is no outstanding missing-TRTEDT case in the current code.</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Used available TRTEDT values; documented subjects with missing TRTEDT.</t>
+          <t>No missing TRTEDT cases remain in the current code (see 'Missing TRTEDT' row above) - the RFENDTC fallback in 03_build_adsl.sas resolved this in an earlier iteration.</t>
         </is>
       </c>
     </row>
@@ -3668,17 +3673,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AD0047, AD0018, SD0054, SD0060, SD1324 - variable/label completeness vs. Define.xml (ADSL/ADAE/ADTTE combined: ~90 occurrences)</t>
+          <t>AD0047, AD0018, SD0054, SD0060, SD1324 - variable/label completeness vs. Define.xml (ADSL/ADAE/ADTTE combined: 118 total finding occurrences)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>This project intentionally built only the most common ADaM variables (per the Module 0 beginner scope), not the full sponsor variable list. Pinnacle 21 therefore flags: standard-required variables this project did not build (AD0047), a few label wording differences vs. the ADaM standard (AD0018), variables the sponsor's Define.xml documents that this trimmed dataset doesn't include (SD0054), a few variables present in the dataset but not in that Define.xml (SD0060), and label wording differences between dataset and Define.xml (SD1324).</t>
+          <t>This project intentionally built only the most common ADaM variables (per the Module 0 beginner scope), not the full sponsor variable list. Pinnacle 21 therefore flags: standard-required variables this project did not build (AD0047), a few label wording differences vs. the ADaM standard (AD0018), variables the sponsor's Define.xml documents that this trimmed dataset doesn't include (SD0054), a few variables present in the dataset but not in that Define.xml (SD0060), and label wording differences between dataset and Define.xml (SD1324). The 118 total reflects individual Pinnacle 21 finding occurrences, not 118 independent errors - several occurrences can arise from the same underlying scope/metadata gap, and the individual counts are available in the Pinnacle 21 Issue Summary report.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Expected and documented - full variable/Define.xml completeness was out of scope for this beginner-level project by design (see Module 0 checklist: "most common variables only").</t>
+          <t>Reviewed and documented as project-scope/metadata findings, not defects - full variable/Define.xml completeness was out of scope for this beginner-level project by design (see Module 0 checklist: "most common variables only"). Referred to as "finding occurrences," not "errors," consistent with Pinnacle 21's own terminology; no attempt was made to represent the project as regulatory-compliant.</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3742,332 +3747,214 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Library setup</t>
+          <t>Library structure</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>04, 05, 10, 16, 18, 19 were missing LIBNAME statements (some only worked if run right after another program in the same SAS session).</t>
+          <t>An early draft risked comparing derived data to itself if reference and derived datasets shared one library.</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Added explicit %let HOME and LIBNAME statements to every program so each one can be run stand-alone.</t>
+          <t>The current code uses three separate libraries in every relevant program: SDTM (raw domains), REF (untouched sponsor reference ADaM datasets), and ADAM (this project's own derived datasets). Every PROC COMPARE in 03/04/05_build_*.sas uses base=REF.xxx (reference) vs compare=ADAM.xxx (ours).</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Reflects current repo (01_setup.sas - 11_export.sas)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Reference vs. derived data (biggest issue)</t>
+          <t>QC integrated into build programs</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>The final derived datasets were saved as ADAM.ADSL / ADAM.ADAE / ADAM.ADTTE - the SAME names as the sponsor's original reference datasets in the ADAM library. This meant PROC COMPARE in 10 and the missing compare in 14 were effectively comparing our own derived data to itself, not to an independent reference.</t>
+          <t>Earlier drafts of this project used separate QC/validation programs apart from the build programs.</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Split into two libraries: DERIVED (everything we build, including the final ADSL/ADAE/ADTTE) and ADAM (kept as the untouched sponsor reference, used only in the QC/validation programs). PROC COMPARE now always uses base=ADAM.xxx (reference) vs compare=DERIVED.xxx (ours).</t>
+          <t>In the delivered repo, each of 03_build_adsl.sas, 04_build_adae.sas, and 05_build_adtte.sas contains its own duplicate-check, missing-value check, logic checks, and PROC COMPARE section against the reference, rather than a separate validation file per dataset.</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Fixed - most important fix in the whole review</t>
+          <t>Reflects current repo - see Project structure in README</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>ADSL had no QC program</t>
+          <t>Program consolidation</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>ADAE and ADTTE each had their own validation program (10, 14), but ADSL jumped straight from build (04-05) to AE exploration (07) with no ADSL QC/PROC COMPARE step.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Added a new program, 06_validation_adsl.sas, following the same duplicate-check / missing-value / PROC COMPARE pattern as the other two datasets.</t>
+          <t>The delivered project consolidates into 11 programs: 01_setup.sas, 02_explore_sdtm.sas, 03/04/05_build_ADSL/ADAE/ADTTE.sas (each with embedded QC + PROC COMPARE), 06_tlf_dataexploration.sas, 07/08/09 summary tables, 10_km_*.sas (Kaplan-Meier plot), and 11_export.sas.</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Fixed - new file added</t>
+          <t>Current repo structure as published on GitHub</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>ADTTE validation had no PROC COMPARE</t>
+          <t>File naming - Resolved</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>14_validation_adtte.sas did every QC check except the actual PROC COMPARE against the reference dataset.</t>
+          <t>An earlier draft had a typo, programs/10_km_attde.sas, that did not match the README's 'Project structure' section (10_km_adtte.sas).</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Added a PROC COMPARE section at the end of 14, base=ADAM.ADTTE vs compare=DERIVED.ADTTE.</t>
+          <t>The Kaplan-Meier program is now named 10_km_adtte.sas, consistent with the ADTTE dataset naming convention and the README. The earlier 10_km_attde.sas typo has been corrected in the repository.</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Resolved - matches current repo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Downstream programs pointed at intermediate STEP datasets</t>
+          <t>11_export.sas self-contained - Resolved</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>09 (ADAE build), 12 (ADTTE build), and the three TLF programs (15, 16, 18, 19) merged/read from ADSL_STEP4 / ADAE_STEP5 instead of the final, renamed ADSL / ADAE datasets.</t>
+          <t>11_export.sas previously read from the ADAM library (e.g. 'set ADAM.ADSL;') without declaring its own 'libname ADAM ...', unlike every other program in the repo, so it only worked if run in the same SAS session right after an earlier program.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>All downstream programs now reference the final DERIVED.ADSL / DERIVED.ADAE datasets, matching the intent of the 'rename to final name' step already present in 05, 09 and 13.</t>
+          <t>11_export.sas now declares '%let HOME=/home/&amp;sysuserid;' and 'libname ADAM "&amp;HOME/sas_adam_project_1";' at the top of the program, so it can be run independently of the preceding SAS programs, provided the ADaM datasets already exist in the specified ADAM library.</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Resolved - matches current repo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Dead / unused code</t>
+          <t>TRT01A source decision</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>05_build_adslstep2.sas created a dataset (EX_BYGROUP) using first./last. that was never used again.</t>
+          <t>An earlier iteration sourced TRT01A from DM.ACTARM, which differed from the reference for a subset of subjects due to dose titration.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Removed - it added confusion without contributing to the final ADSL.</t>
+          <t>The current 03_build_adsl.sas sources TRT01A from DM.ARM, the same field as TRT01P. PROC COMPARE against the reference ADSL returns 0 unequal TRT01A records across all 254 subjects - independently re-verified against the raw CDISC Pilot data. See 'TRT01A Source' in the Reference Differences tab.</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Resolved - matches current code</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Ordering bug</t>
+          <t>TRTEMFL coding convention</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>17_validationdemo.sas printed TEAE_SUMMARY, but that dataset is only created later in 18_tabletret.sas - running 17 on its own (or before 18) would error.</t>
+          <t>Pinnacle 21's generic ADaM CT check (AD0269/CT2001) expects a Y/null flag for TRTEMFL; this study's own Define.xml specifies Y/N.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Removed that print from 17; added a small quick-look print of TEAE_SUMMARY directly inside 18, right after it is created.</t>
+          <t>TRTEMFL is implemented as Y/N per the Define.xml formula (no TRTEDT upper bound). Independently re-verified by replicating this logic against the raw CDISC Pilot AE/EX data - 0 mismatches vs. the reference ADAE. A Y/null alternative was tried and reverted because it broke reconciliation. AD0269/CT2001 is documented as an accepted, justified finding rather than silenced.</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Resolved - matches current code; finding documented, not silenced</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Missing label</t>
+          <t>Partial AE date imputation</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>TRTDUR (treatment duration) was calculated in ADSL but never given a label.</t>
+          <t>Partial AE start dates (YYYY-MM) and all partial/missing end dates needed a documented, bounded approach for a beginner-scope project.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Added label 'Total Treatment Duration (Days)'.</t>
+          <t>YYYY-MM start dates are imputed to day 01; YYYY-only start dates and all partial/missing end dates are left missing. No further CDISC-style imputation was implemented - documented as an explicit scope decision, not an oversight.</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Beyond beginner scope - documented, not implemented</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Unnecessary complexity</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>04_build_adsl_step1.sas used a RETAIN statement that wasn't actually needed (DM has one row per subject, nothing needs to carry across rows).</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Removed the RETAIN statement to keep the program easier to explain in an interview.</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>File renamed for clarity</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>07_data_explorationae1.sas, 11_data_explorationadtte1.sas, 15_tlf1_dataex_ploration.sas, 16_tabletret.sas, 18_tabletret.sas, 05_build_adslstep2.sas had inconsistent/typo'd names.</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Renamed to 07_data_exploration_ae.sas, 11_data_exploration_adtte.sas, 15_tlf1_data_exploration.sas, 16_table_demographics.sas, 18_table_teae.sas, 05_build_adsl_step2.sas.</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Fixed (naming only, no logic change)</t>
-        </is>
-      </c>
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Reference dataset path (Resolved)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>An earlier review round flagged that the sponsor reference ADSL/ADAE/ADTTE files had not yet been supplied, so the separate ADAM (reference) vs DERIVED library pattern could not be test-run end to end.</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>The reference CDISC Pilot ADaM datasets were subsequently placed in the ADAM library path, and PROC COMPARE was re-run for all three datasets. Current logs show 0 unequal records for ADSL (254 subjects), ADAE (1,191 records), and ADTTE (254 subjects) - see the PROC COMPARE sections in 03/04/05_build_*.sas.</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Resolved - reference data obtained and reconciliation completed</t>
-        </is>
-      </c>
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Dose-titration TRT01A mismatch (Historical - resolved in current version)</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>An earlier version of ADSL sourced TRT01A from DM.ACTARM, which showed a 12-of-254-subject difference vs. the reference due to dose titration (the reference reflects the maximum dose a subject ever received).</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>The current code (03_build_adsl.sas) sources TRT01A from DM.ARM, the same field as TRT01P, instead of ACTARM. PROC COMPARE against the reference ADSL now returns 0 unequal TRT01A records across all 254 subjects. See 'TRT01A Source (Resolved - matches reference exactly)' in the Reference Differences tab.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Resolved - superseded by current DM.ARM-based implementation</t>
-        </is>
-      </c>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>TRTEDT/TRTDUR mismatch for 2 subjects (Historical - resolved in current version)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>An earlier PROC COMPARE run showed the reference ADSL had a later TRTEDT than MAX(EXENDTC) for 2 subjects.</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Re-verified with an independent PROC SQL MAX() aggregation. The current PROC COMPARE run of ADSL against the reference shows 0 unequal records across all compared variables, including TRTEDT and TRTDUR, for all 254 subjects. See the matching row in the Reference Differences tab.</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Resolved - no outstanding TRTEDT/TRTDUR discrepancy in the current code</t>
-        </is>
-      </c>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Full re-derivation / imputation</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Partial AE dates (YYYY-MM, YYYY) were left missing rather than imputed to a full date.</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>This is a deliberate, documented scope decision for a beginner project - CDISC has formal AE date imputation rules that are more advanced than what's needed here.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Beyond beginner scope - documented, not implemented</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TRTEMFL logic - regression during Pinnacle21 cleanup</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>While clearing the AD0269/CT2001 Pinnacle21 finding, TRTEMFL was changed from Y/N to Y/blank without an upper bound on TRTEDT. This cleared the Pinnacle21 finding but caused ~35 additional PROC COMPARE mismatches vs. the reference ADAE (65 -&gt; 100), including 10+ records where a real treatment-emergent 'Y' event was incorrectly reset to blank, and 2 downstream AOCC01FL mismatches.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Reverted TRTEMFL to the exact Define.xml formula (Y if ASTDT&gt;=TRTSDT and both non-missing, else N - no TRTEDT bound). PROC COMPARE against reference ADAE returns 0 unequal records for both TRTEMFL and AOCC01FL. AD0269/CT2001 documented as an accepted Pinnacle21 finding, not a code defect (see Pinnacle 21 Validation and Reference Differences sheets).</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fixed - reverted to Define.xml logic; finding documented, not silenced</t>
-        </is>
-      </c>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
